--- a/research/kalshi/frankie_boss/artifacts/Frankie_BOSS_Build_Plan_R4_20260921.xlsx
+++ b/research/kalshi/frankie_boss/artifacts/Frankie_BOSS_Build_Plan_R4_20260921.xlsx
@@ -3052,7 +3052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N40"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.21999979019165" customWidth="1" min="1" max="1"/>
@@ -5706,6 +5706,222 @@
       <c r="N40" s="123" t="inlineStr">
         <is>
           <t>CLAUDE_HANDOFF_20260920.md 08:00Z-09:4xZ 09-21; deploy/aws/box/*; commit 76400157; deploy/aws/box/frankie_box_boss_session.py labels stage: the source contract detector reproduces the first run 29/29 timing labels (2026-09-21)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="123" t="inlineStr">
+        <is>
+          <t>C36</t>
+        </is>
+      </c>
+      <c r="B41" s="123" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C41" s="123" t="inlineStr">
+        <is>
+          <t>Scientific teacher (the experiment's lessons stage)</t>
+        </is>
+      </c>
+      <c r="D41" s="123" t="inlineStr">
+        <is>
+          <t>frankie_box_scientific_teacher.py/.sh, run by the experiment orchestrator's lessons stage after each discovery batch: Frankie's novel findings (only dipole_novel_findings of his classroom ledgers, R09), Jev's JEV_CLAIMS_V1 and the historical claims H01-H10, each tested on the search's counts per discovery day with its circular-shift chance check; writes FRANKIE_LESSONS_V1 into his brain as &lt;day&gt;-lessons, JEV_LESSONS_V1 to Jev's brain, HISTORICAL_LESSONS_V1 kept. On a classroom-arm day without plan ledgers it reads that day's classroom ledgers.json (novel findings only).</t>
+        </is>
+      </c>
+      <c r="E41" s="123" t="inlineStr">
+        <is>
+          <t>The scientific teacher seat (SPEC-scientific-teacher.md): mechanism and evidence; every claim a hypothesis with its own chance check; counts per cell and day, the disposition word orientation only (R14); "the data is showing this instead" (R07); untested combinations listed, never dropped (R13).</t>
+        </is>
+      </c>
+      <c r="F41" s="123" t="inlineStr">
+        <is>
+          <t>Built 2026-09-29; not run on the box.</t>
+        </is>
+      </c>
+      <c r="G41" s="123" t="inlineStr">
+        <is>
+          <t>Built - software; not run</t>
+        </is>
+      </c>
+      <c r="H41" s="123" t="inlineStr">
+        <is>
+          <t>First discovery batch on Greg's go; Dipole components as a search source on every day; conditions not searched yet.</t>
+        </is>
+      </c>
+      <c r="I41" s="123" t="inlineStr">
+        <is>
+          <t>Evidence authority for claims (counts); never a grade (fact grading stays the deterministic classroom grade).</t>
+        </is>
+      </c>
+      <c r="J41" s="123" t="inlineStr">
+        <is>
+          <t>Never a model voice (R17); never reads Frankie's decision process or graded outcomes (R09, R10); never a confirmation day (R15); never pools days or averages (R04, R05).</t>
+        </is>
+      </c>
+      <c r="K41" s="123" t="inlineStr">
+        <is>
+          <t>Experiment (discovery days)</t>
+        </is>
+      </c>
+      <c r="L41" s="123" t="inlineStr">
+        <is>
+          <t>8 - Evaluation</t>
+        </is>
+      </c>
+      <c r="M41" s="123" t="inlineStr">
+        <is>
+          <t>Experiment search (frankie_box_experiment_search.py); C14-C16 teacher rows</t>
+        </is>
+      </c>
+      <c r="N41" s="123" t="inlineStr">
+        <is>
+          <t>deploy/aws/box/frankie_box_scientific_teacher.py; SPEC-scientific-teacher.md; knowledge/CLASSROOM_RULES_V1.json; deploy/aws/box/frankie_box_experiment.py (stage order fetch, ingest, external, root, teacher, classroom, jev, data, search, lessons, exchange, voice, school, reports)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="123" t="inlineStr">
+        <is>
+          <t>C37</t>
+        </is>
+      </c>
+      <c r="B42" s="123" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C42" s="123" t="inlineStr">
+        <is>
+          <t>Three-way exchange (BOSS teacher, scientific teacher, Frankie)</t>
+        </is>
+      </c>
+      <c r="D42" s="123" t="inlineStr">
+        <is>
+          <t>Built 2026-09-29, not run: the orchestrator's exchange stage per classroom-arm discovery day, after the batch's lessons and the day's search. Per scientific-teacher result on a claim: turn 1 the BOSS teacher from its own Dipole rows (step counts, first-to-last relation, Pearson with its overlap; masks: non-PRESENT state pairings, ABLATED / INVALID cursors; control: its own cursor axis), turn 2 the scientific teacher with the search counts per day and the proposed tests listed untested, turn 3 Frankie's code (resolved in his words or kept as a hypothesis, remaining disagreement explicit). Reuses the dipole_teacher_discussion roles, positions, schemas and validators (parse_teacher, parse_frankie). Files exchange.json + exchange-frankie.json + receipt under &lt;run&gt;/exchange/&lt;day&gt;/ and his brain entry &lt;day&gt;-exchange; CLASSROOM / FRANKIE REPORT #N follow it (N reserved after the classroom, unchanged).</t>
+        </is>
+      </c>
+      <c r="E42" s="123" t="inlineStr">
+        <is>
+          <t>SPEC-scientific-teacher.md step 5: the teachers tied, each turn building on the other's; a combination both teachers measure the same way is filed as the teachers' own finding (HYPOTHESIS, scoped, day named); Frankie taught from it.</t>
+        </is>
+      </c>
+      <c r="F42" s="123" t="inlineStr">
+        <is>
+          <t>Built 2026-09-29; not run on the box.</t>
+        </is>
+      </c>
+      <c r="G42" s="123" t="inlineStr">
+        <is>
+          <t>Built - software; not run</t>
+        </is>
+      </c>
+      <c r="H42" s="123" t="inlineStr">
+        <is>
+          <t>Run on the first classroom-arm discovery days on Greg's go. The voice stage beside it is a stub (records waiting, not wired): voicing the discussion with a model needs Greg's own confirmation of an R17 amendment, its component row and the Pod; the exchange's voice_turns and the voice validator (frankie_box_exchange_voice.py, code only) are ready.</t>
+        </is>
+      </c>
+      <c r="I42" s="123" t="inlineStr">
+        <is>
+          <t>Teaching authority on what was measured jointly; the BOSS teacher's targets are never changed by it.</t>
+        </is>
+      </c>
+      <c r="J42" s="123" t="inlineStr">
+        <is>
+          <t>Never a model voice (R17); the teachers never see Frankie's decision process or graded outcomes (R09, R10); Jev's claims only as labelled claims and never in Frankie's view or brain; counts never averages; zero data dropped (R04).</t>
+        </is>
+      </c>
+      <c r="K42" s="123" t="inlineStr">
+        <is>
+          <t>Experiment (classroom-arm discovery days)</t>
+        </is>
+      </c>
+      <c r="L42" s="123" t="inlineStr">
+        <is>
+          <t>8 - Evaluation</t>
+        </is>
+      </c>
+      <c r="M42" s="123" t="inlineStr">
+        <is>
+          <t>C36; C14-C16 teacher rows; the classroom arm</t>
+        </is>
+      </c>
+      <c r="N42" s="123" t="inlineStr">
+        <is>
+          <t>deploy/aws/box/frankie_box_experiment_exchange.py/.sh; frankie_box_classroom_code.exchange_reply; research/kalshi/frankie_boss/dipole_teacher_discussion.py; SPEC-scientific-teacher.md; knowledge/CLASSROOM_RULES_V1.json; deploy/aws/box/frankie_box_experiment.py (stage order fetch, ingest, external, root, teacher, classroom, jev, data, search, lessons, exchange, voice, school, reports)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="123" t="inlineStr">
+        <is>
+          <t>C38</t>
+        </is>
+      </c>
+      <c r="B43" s="123" t="inlineStr">
+        <is>
+          <t>Experiment</t>
+        </is>
+      </c>
+      <c r="C43" s="123" t="inlineStr">
+        <is>
+          <t>Frankie's school knowledge base (FRANKIE_SCHOOL_KNOWLEDGE_V1)</t>
+        </is>
+      </c>
+      <c r="D43" s="123" t="inlineStr">
+        <is>
+          <t>Built 2026-09-29, not run: the orchestrator's school stage per classroom-arm day after the exchange (never Monday 20211004): ONE file &lt;brain&gt;/school/&lt;day&gt;.json with sections frankie_classwork, boss_teacher, scientific_teacher, exchange, day_file (each labelled with its author; every item with source path and sha256; inline JSON, a stated subset, or a pointer), plus the append-only &lt;brain&gt;/school/index.json (day, file, sha256, bytes, report number N). The brain loader and the next classroom day (Frankie's code: reproduction of earlier hypotheses) read every earlier day's file.</t>
+        </is>
+      </c>
+      <c r="E43" s="123" t="inlineStr">
+        <is>
+          <t>Each later school day learns from all earlier days' school JSON, within the brain's include / unavailable conventions.</t>
+        </is>
+      </c>
+      <c r="F43" s="123" t="inlineStr">
+        <is>
+          <t>Built 2026-09-29; not run on the box.</t>
+        </is>
+      </c>
+      <c r="G43" s="123" t="inlineStr">
+        <is>
+          <t>Built - software; not run</t>
+        </is>
+      </c>
+      <c r="H43" s="123" t="inlineStr">
+        <is>
+          <t>Run after the first exchange on Greg's go; the discussion section waits on the voice decision (listed missing).</t>
+        </is>
+      </c>
+      <c r="I43" s="123" t="inlineStr">
+        <is>
+          <t>Knowledge carried between school days; never an answer key.</t>
+        </is>
+      </c>
+      <c r="J43" s="123" t="inlineStr">
+        <is>
+          <t>Never the answer key or the exhaustive grade (R10: only WHERE he was corrected); never Jev's claims; never overwritten (a day with other bytes declines, R16); missing listed with the reason.</t>
+        </is>
+      </c>
+      <c r="K43" s="123" t="inlineStr">
+        <is>
+          <t>Experiment (classroom-arm days)</t>
+        </is>
+      </c>
+      <c r="L43" s="123" t="inlineStr">
+        <is>
+          <t>8 - Evaluation</t>
+        </is>
+      </c>
+      <c r="M43" s="123" t="inlineStr">
+        <is>
+          <t>C37; C36; the classroom arm</t>
+        </is>
+      </c>
+      <c r="N43" s="123" t="inlineStr">
+        <is>
+          <t>deploy/aws/box/frankie_box_school_knowledge.py/.sh; frankie_box_brain.write_school_day / school_rows / load; SPEC-scientific-teacher.md; knowledge/CLASSROOM_RULES_V1.json; deploy/aws/box/frankie_box_experiment.py (stage order fetch, ingest, external, root, teacher, classroom, jev, data, search, lessons, exchange, voice, school, reports)</t>
         </is>
       </c>
     </row>
@@ -7468,7 +7684,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7.21999979019165" customWidth="1" min="1" max="1"/>
@@ -8922,6 +9138,110 @@
       <c r="J31" s="123" t="inlineStr">
         <is>
           <t>Execution</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="21.60000038146973" customHeight="1">
+      <c r="A32" s="123" t="inlineStr">
+        <is>
+          <t>G27</t>
+        </is>
+      </c>
+      <c r="B32" s="123" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="C32" s="123" t="inlineStr">
+        <is>
+          <t>The scientific teacher's lessons, the three-way exchange and the school knowledge base are code: model_calls 0 in every lessons file, exchange file, school file and receipt; each turn labelled with its author (R11, R17). The voice stage stays not wired until Greg confirms an R17 amendment.</t>
+        </is>
+      </c>
+      <c r="D32" s="123" t="inlineStr">
+        <is>
+          <t>C36, C37, C38</t>
+        </is>
+      </c>
+      <c r="E32" s="123" t="inlineStr">
+        <is>
+          <t>Receipts with model_calls 0; the voice receipts record not_wired</t>
+        </is>
+      </c>
+      <c r="F32" s="123" t="inlineStr">
+        <is>
+          <t>Built - software; not run</t>
+        </is>
+      </c>
+      <c r="G32" s="123" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H32" s="123" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I32" s="123" t="inlineStr">
+        <is>
+          <t>Refuse the turn; nothing filed into a brain.</t>
+        </is>
+      </c>
+      <c r="J32" s="123" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="21.60000038146973" customHeight="1">
+      <c r="A33" s="123" t="inlineStr">
+        <is>
+          <t>G28</t>
+        </is>
+      </c>
+      <c r="B33" s="123" t="inlineStr">
+        <is>
+          <t>Classroom</t>
+        </is>
+      </c>
+      <c r="C33" s="123" t="inlineStr">
+        <is>
+          <t>The teachers never see Frankie's decision process or graded outcomes (R09, R10); discovery days only (R15); Jev's claims never in Frankie's replies, view, brain or school; counts per day, never pooled or averaged; zero data dropped (R04, R05).</t>
+        </is>
+      </c>
+      <c r="D33" s="123" t="inlineStr">
+        <is>
+          <t>C36, C37, C38</t>
+        </is>
+      </c>
+      <c r="E33" s="123" t="inlineStr">
+        <is>
+          <t>The exchange and school files: withheld and missing lists, jev_withheld counts, per-day counts</t>
+        </is>
+      </c>
+      <c r="F33" s="123" t="inlineStr">
+        <is>
+          <t>Built - software; not run</t>
+        </is>
+      </c>
+      <c r="G33" s="123" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="H33" s="123" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="I33" s="123" t="inlineStr">
+        <is>
+          <t>Decline the step with the reason; the run goes on.</t>
+        </is>
+      </c>
+      <c r="J33" s="123" t="inlineStr">
+        <is>
+          <t>Evaluation</t>
         </is>
       </c>
     </row>
@@ -10820,7 +11140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F132"/>
+  <dimension ref="A1:F137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -14668,6 +14988,136 @@
         </is>
       </c>
     </row>
+    <row r="133">
+      <c r="A133" s="130" t="inlineStr">
+        <is>
+          <t>Components</t>
+        </is>
+      </c>
+      <c r="B133" s="130" t="n">
+        <v>41</v>
+      </c>
+      <c r="C133" s="130" t="inlineStr">
+        <is>
+          <t>A41:N41</t>
+        </is>
+      </c>
+      <c r="D133" s="130" t="n"/>
+      <c r="E133" s="130" t="inlineStr">
+        <is>
+          <t>Scientific teacher (the experiment's lessons stage)</t>
+        </is>
+      </c>
+      <c r="F133" s="130" t="inlineStr">
+        <is>
+          <t>new component row 2026-09-29 (Greg's go for the three-way exchange build; code only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="130" t="inlineStr">
+        <is>
+          <t>Components</t>
+        </is>
+      </c>
+      <c r="B134" s="130" t="n">
+        <v>42</v>
+      </c>
+      <c r="C134" s="130" t="inlineStr">
+        <is>
+          <t>A42:N42</t>
+        </is>
+      </c>
+      <c r="D134" s="130" t="n"/>
+      <c r="E134" s="130" t="inlineStr">
+        <is>
+          <t>Three-way exchange (BOSS teacher, scientific teacher, Frankie)</t>
+        </is>
+      </c>
+      <c r="F134" s="130" t="inlineStr">
+        <is>
+          <t>new component row 2026-09-29 (Greg's go for the three-way exchange build; code only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="130" t="inlineStr">
+        <is>
+          <t>Components</t>
+        </is>
+      </c>
+      <c r="B135" s="130" t="n">
+        <v>43</v>
+      </c>
+      <c r="C135" s="130" t="inlineStr">
+        <is>
+          <t>A43:N43</t>
+        </is>
+      </c>
+      <c r="D135" s="130" t="n"/>
+      <c r="E135" s="130" t="inlineStr">
+        <is>
+          <t>Frankie's school knowledge base (FRANKIE_SCHOOL_KNOWLEDGE_V1)</t>
+        </is>
+      </c>
+      <c r="F135" s="130" t="inlineStr">
+        <is>
+          <t>new component row 2026-09-29 (Greg's go for the three-way exchange build; code only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="130" t="inlineStr">
+        <is>
+          <t>Gates</t>
+        </is>
+      </c>
+      <c r="B136" s="130" t="n">
+        <v>32</v>
+      </c>
+      <c r="C136" s="130" t="inlineStr">
+        <is>
+          <t>A32:J32</t>
+        </is>
+      </c>
+      <c r="D136" s="130" t="n"/>
+      <c r="E136" s="130" t="inlineStr">
+        <is>
+          <t>G27 Classroom</t>
+        </is>
+      </c>
+      <c r="F136" s="130" t="inlineStr">
+        <is>
+          <t>new gate row 2026-09-29 (the three-way exchange build; code only)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="130" t="inlineStr">
+        <is>
+          <t>Gates</t>
+        </is>
+      </c>
+      <c r="B137" s="130" t="n">
+        <v>33</v>
+      </c>
+      <c r="C137" s="130" t="inlineStr">
+        <is>
+          <t>A33:J33</t>
+        </is>
+      </c>
+      <c r="D137" s="130" t="n"/>
+      <c r="E137" s="130" t="inlineStr">
+        <is>
+          <t>G28 Classroom</t>
+        </is>
+      </c>
+      <c r="F137" s="130" t="inlineStr">
+        <is>
+          <t>new gate row 2026-09-29 (the three-way exchange build; code only)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
